--- a/artfynd/A 32709-2021 artfynd.xlsx
+++ b/artfynd/A 32709-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32709-2021 artfynd.xlsx
+++ b/artfynd/A 32709-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>162529</v>
       </c>
       <c r="B2" t="n">
-        <v>104642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500315.0785221145</v>
+        <v>500315</v>
       </c>
       <c r="R2" t="n">
-        <v>6515604.261078031</v>
+        <v>6515604</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>T-Ask-0524</t>
+          <t>Arkiv-T-Ask-0008</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,19 +752,9 @@
           <t>2009-08-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,63 +784,54 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7118596</v>
+        <v>63649388</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sänna, Nrk</t>
+          <t>Nykyrka/Brattebrobacke, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499980.0750528314</v>
+        <v>499875</v>
       </c>
       <c r="R3" t="n">
-        <v>6515533.220569805</v>
+        <v>6515507</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,27 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Anders Hedlund  ID;30151</t>
+          <t>Calluna AB</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,136 +880,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Olof Rosenqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7129024</v>
-      </c>
-      <c r="B4" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219686</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vätteros</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lathraea squamaria</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sänna, Nrk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>499980.0750528314</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6515533.220569805</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Askersund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hammar</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Anders Hedlund  ID;30152</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
